--- a/Luban/Config/Datas/Levels/L12/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L12/EnemyList.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>L12 W1/25; N=42; EHP=251.328000; normal:17x21,normal:18x21</t>
+          <t>L12 W1/25; N=42; EHP=568.932815; normal:17x21,normal:18x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>L12 W2/25; N=48; EHP=300.760627; normal:17x24,normal:18x24</t>
+          <t>L12 W2/25; N=48; EHP=680.833772; normal:17x24,normal:18x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>3544136,3544673,3544019,3544136,3544673,3544091,3544136,3544673,3544099,3544136,3544673,3544099,3544136,3544673,3544107,3544136,3544673,3544115,3544136,3544673,3544136,3544673,3544136,3544673,3544136,3544673,3544136,3544673,3544136,3544673,3544136,3544673,3544136,3544673,3544136,3544673,3544136,3544136,3544144,3544144,3544144,3544144,3544144,3544144,3544144,3544144,3544144,3544144,3544144,3544144,3544144,3544144,3544144,3544144</t>
+          <t>3544136,3544673,3544136,3544673,3544136,3544673,3544136,3544673,3544136,3544673,3544136,3544673,3544136,3544673,3544136,3544673,3544136,3544673,3544136,3544673,3544136,3544673,3544136,3544673,3544136,3544673,3544136,3544673,3544136,3544673,3544136,3544136,3544144,3544144,3544144,3544144,3544144,3544144,3544144,3544144,3544144,3544144,3544144,3544144,3544144,3544144,3544144,3544144,3544136,3544136,3544136,3544136,3544136,3544136</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>L12 W3/25; N=54; EHP=374.320742; air:2x1,air:11x1,air:12x2,air:13x1,air:14x1,normal:17x17,normal:18x16,swarm:84x15</t>
+          <t>L12 W3/25; N=54; EHP=908.876208; normal:17x23,normal:18x16,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>3546136,3546673,3546019,3546136,3546673,3546019,3546136,3546673,3546091,3546136,3546673,3546099,3546136,3546673,3546107,3546136,3546673,3546107,3546136,3546673,3546115,3546136,3546673,3546136,3546673,3546136,3546673,3546136,3546673,3546136,3546673,3546136,3546673,3546136,3546673,3546136,3546673,3546136,3546673,3546136,3546136,3546144,3546144,3546144,3546144,3546144,3546144,3546144,3546144,3546144,3546144,3546144,3546144,3546144,3546144,3546144,3546144,3546144,3546144,3546144</t>
+          <t>3546136,3546673,3546136,3546673,3546136,3546673,3546136,3546673,3546136,3546673,3546136,3546673,3546136,3546673,3546136,3546673,3546136,3546673,3546136,3546673,3546136,3546673,3546136,3546673,3546136,3546673,3546136,3546673,3546136,3546673,3546136,3546673,3546136,3546136,3546144,3546144,3546144,3546144,3546144,3546144,3546144,3546144,3546144,3546144,3546144,3546144,3546144,3546144,3546144,3546144,3546144,3546144,3546144,3546144,3546144,3546144,3546144,3546144,3546144,3546144</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>L12 W4/25; N=60; EHP=478.923456; air:2x2,air:11x1,air:12x1,air:13x2,air:14x1,normal:17x18,normal:18x19,swarm:84x16</t>
+          <t>L12 W4/25; N=60; EHP=1166.712783; normal:17x18,normal:18x26,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>3548136,3548673,3548019,3548668,3548136,3548673,3548091,3548668,3548136,3548673,3548091,3548668,3548136,3548673,3548099,3548868,3548136,3548673,3548107,3548868,3548136,3548673,3548107,3548868,3548136,3548673,3548115,3548988,3548136,3548673,3548115,3548988,3548136,3548673,3548988,3548136,3548673,3548136,3548673,3548136,3548673,3548136,3548673,3548136,3548673,3548136,3548673,3548136,3548673,3548144,3548673,3548144,3548673,3548144,3548144,3548144,3548144,3548144,3548144,3548144,3548144,3548144,3548144,3548144,3548144,3548144</t>
+          <t>3548136,3548019,3548019,3548668,3548136,3548091,3548091,3548668,3548136,3548091,3548091,3548668,3548136,3548099,3548099,3548868,3548136,3548107,3548107,3548868,3548136,3548107,3548107,3548868,3548136,3548115,3548115,3548988,3548136,3548115,3548115,3548988,3548136,3548673,3548988,3548136,3548673,3548136,3548673,3548136,3548673,3548136,3548673,3548136,3548673,3548136,3548673,3548136,3548673,3548144,3548673,3548144,3548673,3548144,3548144,3548144,3548144,3548144,3548144,3548144,3548144,3548144,3548144,3548144,3548144,3548144</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L12 W5/25; N=66; EHP=907.366462; air:2x1,air:11x2,air:12x1,air:13x2,air:14x2,normal:17x16,normal:18x15,medium:83x3,swarm:84x18,medium:108x3,medium:123x3</t>
+          <t>L12 W5/25; N=66; EHP=2080.686787; air:2x2,air:11x4,air:12x2,air:13x4,air:14x4,medium:83x3,medium:108x3,medium:123x3,normal:17x16,normal:18x15,swarm:84x10 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>3550136,3550673,3550242,3550019,3550668,3550136,3550673,3550242,3550019,3550668,3550136,3550673,3550466,3550091,3550668,3550136,3550673,3550466,3550091,3550668,3550136,3550673,3550514,3550099,3550868,3550136,3550673,3550514,3550099,3550868,3550136,3550673,3550786,3550107,3550868,3550136,3550673,3550786,3550115,3550988,3550136,3550673,3550115,3550988,3550136,3550673,3550988,3550136,3550673,3550136,3550673,3550144,3550673,3550144,3550673,3550144,3550673,3550144,3550673,3550144,3550673,3550144,3550673,3550144,3550673,3550144,3550673,3550144,3550144,3550144,3550144,3550144</t>
+          <t>3550136,3550019,3550242,3550019,3550668,3550136,3550019,3550242,3550019,3550668,3550136,3550091,3550466,3550091,3550668,3550136,3550091,3550466,3550091,3550668,3550136,3550099,3550514,3550099,3550868,3550136,3550099,3550514,3550099,3550868,3550136,3550107,3550786,3550107,3550868,3550136,3550115,3550786,3550115,3550988,3550136,3550115,3550115,3550988,3550136,3550673,3550988,3550136,3550673,3550136,3550673,3550144,3550673,3550144,3550673,3550144,3550673,3550144,3550673,3550144,3550673,3550144,3550673,3550144,3550673,3550144,3550673,3550144,3550144,3550144,3550144,3550144</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L12 W6/25; N=72; EHP=926.000000; air:2x2,air:11x2,air:12x2,air:13x1,air:14x2,normal:17x12,normal:18x13,fast:30x2,fast:58x2,fast:64x2,medium:83x4,swarm:84x20,fast:98x2,medium:108x3,medium:123x3</t>
+          <t>L12 W6/25; N=72; EHP=2124.841726; air:2x4,air:11x4,air:12x4,air:13x2,air:14x4,fast:30x2,fast:58x2,fast:64x2,fast:98x2,medium:83x4,medium:108x3,medium:123x3,normal:17x12,normal:18x13,swarm:84x11 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>3552136,3552673,3552242,3552019,3552668,3552136,3552673,3552242,3552019,3552668,3552136,3552673,3552466,3552091,3552668,3552136,3552673,3552466,3552099,3552868,3552136,3552673,3552514,3552099,3552868,3552136,3552673,3552514,3552107,3552868,3552136,3552673,3552514,3552107,3552868,3552136,3552673,3552786,3552115,3552988,3552136,3552673,3552786,3552115,3552988,3552136,3552673,3552988,3552136,3552673,3552988,3552136,3552673,3552136,3552673,3552136,3552673,3552144,3552673,3552144,3552673,3552144,3552673,3552144,3552673,3552144,3552673,3552144,3552673,3552144,3552673,3552144,3552144,3552144,3552144,3552144,3552144,3552144</t>
+          <t>3552136,3552019,3552242,3552019,3552668,3552136,3552019,3552242,3552019,3552668,3552136,3552091,3552466,3552091,3552668,3552136,3552099,3552466,3552099,3552868,3552136,3552099,3552514,3552099,3552868,3552136,3552107,3552514,3552107,3552868,3552136,3552107,3552514,3552107,3552868,3552136,3552115,3552786,3552115,3552988,3552136,3552115,3552786,3552115,3552988,3552136,3552673,3552988,3552136,3552673,3552988,3552136,3552673,3552136,3552673,3552136,3552673,3552144,3552673,3552144,3552673,3552144,3552673,3552144,3552673,3552144,3552673,3552144,3552673,3552144,3552673,3552144,3552144,3552144,3552144,3552144,3552144,3552144</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L12 W7/25; N=78; EHP=1048.138291; air:2x2,air:11x1,air:12x2,air:13x2,air:14x2,normal:17x14,normal:18x14,fast:30x2,fast:58x2,fast:64x3,medium:83x3,swarm:84x21,fast:98x2,medium:108x4,medium:123x4</t>
+          <t>L12 W7/25; N=78; EHP=2402.315298; air:2x4,air:11x2,air:12x4,air:13x4,air:14x4,fast:30x2,fast:58x2,fast:64x3,fast:98x2,medium:83x3,medium:108x4,medium:123x4,normal:17x14,normal:18x14,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>3554136,3554673,3554242,3554019,3554668,3554136,3554673,3554242,3554019,3554668,3554136,3554673,3554242,3554091,3554668,3554136,3554673,3554466,3554091,3554668,3554136,3554673,3554466,3554099,3554868,3554136,3554673,3554514,3554099,3554868,3554136,3554673,3554514,3554107,3554868,3554136,3554673,3554786,3554107,3554868,3554136,3554673,3554786,3554115,3554988,3554136,3554673,3554786,3554115,3554988,3554136,3554673,3554988,3554136,3554673,3554988,3554136,3554673,3554136,3554673,3554144,3554673,3554144,3554673,3554144,3554673,3554144,3554673,3554144,3554673,3554144,3554673,3554144,3554673,3554144,3554673,3554144,3554673,3554144,3554144,3554144,3554144,3554144,3554144</t>
+          <t>3554136,3554019,3554242,3554019,3554668,3554136,3554019,3554242,3554019,3554668,3554136,3554091,3554242,3554091,3554668,3554136,3554091,3554466,3554091,3554668,3554136,3554099,3554466,3554099,3554868,3554136,3554099,3554514,3554099,3554868,3554136,3554107,3554514,3554107,3554868,3554136,3554107,3554786,3554107,3554868,3554136,3554115,3554786,3554115,3554988,3554136,3554115,3554786,3554115,3554988,3554136,3554673,3554988,3554136,3554673,3554988,3554136,3554673,3554136,3554673,3554144,3554673,3554144,3554673,3554144,3554673,3554144,3554673,3554144,3554673,3554144,3554673,3554144,3554673,3554144,3554673,3554144,3554673,3554144,3554144,3554144,3554144,3554144,3554144</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L12 W8/25; N=84; EHP=1349.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x14,normal:18x15,fast:30x3,fast:58x2,fast:64x2,medium:83x4,swarm:84x23,fast:98x3,medium:108x4,medium:123x4</t>
+          <t>L12 W8/25; N=84; EHP=3093.219512; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x3,fast:58x2,fast:64x2,fast:98x3,medium:83x4,medium:108x4,medium:123x4,normal:17x14,normal:18x15,swarm:84x13 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>3556136,3556673,3556242,3556019,3556668,3556136,3556673,3556242,3556019,3556668,3556136,3556673,3556466,3556019,3556668,3556136,3556673,3556466,3556091,3556668,3556136,3556673,3556466,3556091,3556668,3556136,3556673,3556514,3556099,3556868,3556136,3556673,3556514,3556099,3556868,3556136,3556673,3556786,3556107,3556868,3556136,3556673,3556786,3556107,3556868,3556136,3556673,3556786,3556115,3556988,3556136,3556673,3556115,3556988,3556136,3556673,3556988,3556136,3556673,3556988,3556136,3556673,3556136,3556673,3556136,3556673,3556144,3556673,3556144,3556673,3556144,3556673,3556144,3556673,3556144,3556673,3556144,3556673,3556144,3556673,3556144,3556673,3556144,3556673,3556144,3556144,3556144,3556144,3556144,3556144</t>
+          <t>3556136,3556019,3556242,3556019,3556668,3556136,3556019,3556242,3556019,3556668,3556136,3556019,3556466,3556019,3556668,3556136,3556091,3556466,3556091,3556668,3556136,3556091,3556466,3556091,3556668,3556136,3556099,3556514,3556099,3556868,3556136,3556099,3556514,3556099,3556868,3556136,3556107,3556786,3556107,3556868,3556136,3556107,3556786,3556107,3556868,3556136,3556115,3556786,3556115,3556988,3556136,3556115,3556115,3556988,3556136,3556673,3556988,3556136,3556673,3556988,3556136,3556673,3556136,3556673,3556136,3556673,3556144,3556673,3556144,3556673,3556144,3556673,3556144,3556673,3556144,3556673,3556144,3556673,3556144,3556673,3556144,3556673,3556144,3556673,3556144,3556144,3556144,3556144,3556144,3556144</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L12 W9/25; N=90; EHP=1722.000000; air:2x3,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x16,normal:18x15,fast:30x2,fast:58x3,fast:64x2,medium:83x5,swarm:84x25,fast:98x3,medium:108x4,medium:123x4</t>
+          <t>L12 W9/25; N=90; EHP=3949.888896; air:2x6,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x2,fast:58x3,fast:64x2,fast:98x3,medium:83x5,medium:108x4,medium:123x4,normal:17x16,normal:18x15,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>3558136,3558673,3558242,3558019,3558668,3558136,3558673,3558242,3558019,3558668,3558136,3558673,3558242,3558091,3558668,3558136,3558673,3558466,3558091,3558668,3558136,3558673,3558466,3558091,3558868,3558136,3558673,3558466,3558099,3558868,3558136,3558673,3558514,3558099,3558868,3558136,3558673,3558514,3558107,3558868,3558136,3558673,3558514,3558107,3558868,3558136,3558673,3558786,3558107,3558988,3558136,3558673,3558786,3558115,3558988,3558136,3558673,3558115,3558988,3558136,3558673,3558988,3558136,3558673,3558988,3558136,3558673,3558136,3558673,3558144,3558673,3558144,3558673,3558144,3558673,3558144,3558673,3558144,3558673,3558144,3558673,3558144,3558673,3558144,3558673,3558144,3558673,3558144,3558673,3558144,3558144,3558144,3558144,3558144,3558144,3558144</t>
+          <t>3558136,3558019,3558242,3558019,3558668,3558136,3558019,3558242,3558019,3558668,3558136,3558091,3558242,3558091,3558668,3558136,3558091,3558466,3558091,3558668,3558136,3558091,3558466,3558091,3558868,3558136,3558099,3558466,3558099,3558868,3558136,3558099,3558514,3558099,3558868,3558136,3558107,3558514,3558107,3558868,3558136,3558107,3558514,3558107,3558868,3558136,3558107,3558786,3558107,3558988,3558136,3558115,3558786,3558115,3558988,3558136,3558115,3558115,3558988,3558136,3558673,3558988,3558136,3558673,3558988,3558136,3558673,3558136,3558673,3558144,3558673,3558144,3558673,3558144,3558673,3558144,3558673,3558144,3558673,3558144,3558673,3558144,3558673,3558144,3558673,3558144,3558673,3558144,3558673,3558144,3558144,3558144,3558144,3558144,3558144,3558144</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L12 W10/25; N=96; EHP=3178.000000; air:2x2,air:11x3,air:12x2,air:13x3,air:14x2,normal:17x16,normal:18x17,fast:30x3,fast:58x3,fast:64x3,medium:83x4,swarm:84x26,fast:98x2,medium:108x5,medium:123x5</t>
+          <t>L12 W10/25; N=96; EHP=7291.660811; air:2x4,air:11x6,air:12x4,air:13x6,air:14x4,fast:30x3,fast:58x3,fast:64x3,fast:98x2,medium:83x4,medium:108x5,medium:123x5,normal:17x16,normal:18x17,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>3560136,3560673,3560242,3560019,3560668,3560253,3560136,3560673,3560242,3560019,3560668,3560325,3560136,3560673,3560242,3560091,3560668,3560541,3560136,3560673,3560466,3560091,3560668,3560541,3560136,3560673,3560466,3560091,3560668,3560565,3560136,3560673,3560466,3560099,3560868,3560645,3560136,3560673,3560514,3560099,3560868,3560693,3560136,3560673,3560514,3560107,3560868,3560709,3560136,3560673,3560514,3560107,3560868,3560709,3560136,3560673,3560786,3560115,3560868,3561021,3560136,3560673,3560786,3560115,3560988,3560136,3560673,3560786,3560115,3560988,3560136,3560673,3560988,3560144,3560673,3560988,3560144,3560673,3560988,3560144,3560673,3560144,3560673,3560144,3560673,3560144,3560673,3560144,3560673,3560144,3560673,3560144,3560673,3560144,3560673,3560144,3560673,3560144,3560673,3560673,3560673,3560673</t>
+          <t>3560136,3560019,3560242,3560019,3560668,3560253,3560136,3560019,3560242,3560019,3560668,3560325,3560136,3560091,3560242,3560091,3560668,3560541,3560136,3560091,3560466,3560091,3560668,3560541,3560136,3560091,3560466,3560091,3560668,3560565,3560136,3560099,3560466,3560099,3560868,3560645,3560136,3560099,3560514,3560099,3560868,3560693,3560136,3560107,3560514,3560107,3560868,3560709,3560136,3560107,3560514,3560107,3560868,3560709,3560136,3560115,3560786,3560115,3560868,3561021,3560136,3560115,3560786,3560115,3560988,3560136,3560115,3560786,3560115,3560988,3560136,3560673,3560988,3560144,3560673,3560988,3560144,3560673,3560988,3560144,3560673,3560144,3560673,3560144,3560673,3560144,3560673,3560144,3560673,3560144,3560673,3560144,3560673,3560144,3560673,3560144,3560673,3560144,3560673,3560673,3560673,3560673</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L12 W11/25; N=102; EHP=3242.000000; air:2x2,air:11x3,air:12x2,air:13x2,air:14x3,normal:17x13,normal:18x12,fast:30x3,heavy:31x1,heavy:40x1,fast:58x3,fast:64x3,heavy:67x2,heavy:70x1,heavy:80x1,medium:83x5,swarm:84x28,heavy:86x1,heavy:88x2,fast:98x3,medium:108x5,medium:123x5,heavy:127x1</t>
+          <t>L12 W11/25; N=102; EHP=7421.784140; air:2x4,air:11x6,air:12x4,air:13x4,air:14x6,fast:30x3,fast:58x3,fast:64x3,fast:98x3,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x1,heavy:80x1,heavy:86x1,heavy:88x2,heavy:127x1,medium:83x5,medium:108x5,medium:123x5,normal:17x13,normal:18x12,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>3562136,3562673,3562242,3562019,3562668,3562253,3562136,3562673,3562242,3562019,3562668,3562325,3562136,3562673,3562242,3562019,3562668,3562541,3562136,3562673,3562466,3562091,3562668,3562565,3562136,3562673,3562466,3562091,3562668,3562645,3562136,3562673,3562466,3562099,3562668,3562645,3562136,3562673,3562514,3562099,3562868,3562693,3562136,3562673,3562514,3562099,3562868,3562709,3562136,3562673,3562514,3562107,3562868,3562709,3562136,3562673,3562786,3562107,3562868,3563021,3562136,3562673,3562786,3562115,3562868,3562136,3562673,3562786,3562115,3562988,3562136,3562673,3562115,3562988,3562144,3562673,3562988,3562144,3562673,3562988,3562144,3562673,3562988,3562144,3562673,3562144,3562673,3562144,3562673,3562144,3562673,3562144,3562673,3562144,3562673,3562144,3562673,3562144,3562673,3562144,3562673,3562144,3562673,3562144,3562673,3562673,3562673,3562673</t>
+          <t>3562136,3562019,3562242,3562019,3562668,3562253,3562136,3562019,3562242,3562019,3562668,3562325,3562136,3562019,3562242,3562019,3562668,3562541,3562136,3562091,3562466,3562091,3562668,3562565,3562136,3562091,3562466,3562091,3562668,3562645,3562136,3562099,3562466,3562099,3562668,3562645,3562136,3562099,3562514,3562099,3562868,3562693,3562136,3562099,3562514,3562099,3562868,3562709,3562136,3562107,3562514,3562107,3562868,3562709,3562136,3562107,3562786,3562107,3562868,3563021,3562136,3562115,3562786,3562115,3562868,3562136,3562115,3562786,3562115,3562988,3562136,3562115,3562115,3562988,3562144,3562673,3562988,3562144,3562673,3562988,3562144,3562673,3562988,3562144,3562673,3562144,3562673,3562144,3562673,3562144,3562673,3562144,3562673,3562144,3562673,3562144,3562673,3562144,3562673,3562144,3562673,3562144,3562673,3562144,3562673,3562673,3562673,3562673</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L12 W12/25; N=108; EHP=3355.000000; air:2x3,air:11x2,air:12x3,air:13x2,air:14x3,normal:17x13,normal:18x14,fast:30x3,heavy:31x1,heavy:40x1,fast:58x3,fast:64x3,heavy:67x1,heavy:70x1,heavy:80x2,medium:83x6,swarm:84x30,heavy:86x1,heavy:88x2,fast:98x3,medium:108x5,medium:123x5,heavy:127x1</t>
+          <t>L12 W12/25; N=108; EHP=7683.085533; air:2x6,air:11x4,air:12x6,air:13x4,air:14x6,fast:30x3,fast:58x3,fast:64x3,fast:98x3,heavy:31x1,heavy:40x1,heavy:67x1,heavy:70x1,heavy:80x2,heavy:86x1,heavy:88x2,heavy:127x1,medium:83x6,medium:108x5,medium:123x5,normal:17x13,normal:18x14,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>3564136,3564673,3564242,3564019,3564668,3564253,3564136,3564673,3564242,3564019,3564668,3564253,3564136,3564673,3564242,3564019,3564668,3564325,3564136,3564673,3564466,3564091,3564668,3564541,3564136,3564673,3564466,3564091,3564668,3564565,3564136,3564673,3564466,3564091,3564868,3564645,3564136,3564673,3564514,3564099,3564868,3564645,3564136,3564673,3564514,3564099,3564868,3564693,3564136,3564673,3564514,3564099,3564868,3564693,3564136,3564673,3564786,3564107,3564868,3564709,3564136,3564673,3564786,3564107,3564868,3565021,3564136,3564673,3564786,3564107,3564988,3564136,3564673,3564786,3564115,3564988,3564136,3564673,3564115,3564988,3564144,3564673,3564988,3564144,3564673,3564988,3564144,3564673,3564988,3564144,3564673,3564144,3564673,3564144,3564673,3564144,3564673,3564144,3564673,3564144,3564673,3564144,3564673,3564144,3564673,3564144,3564673,3564144,3564673,3564144,3564673,3564673,3564673,3564673</t>
+          <t>3564136,3564019,3564242,3564019,3564668,3564253,3564136,3564019,3564242,3564019,3564668,3564253,3564136,3564019,3564242,3564019,3564668,3564325,3564136,3564091,3564466,3564091,3564668,3564541,3564136,3564091,3564466,3564091,3564668,3564565,3564136,3564091,3564466,3564091,3564868,3564645,3564136,3564099,3564514,3564099,3564868,3564645,3564136,3564099,3564514,3564099,3564868,3564693,3564136,3564099,3564514,3564099,3564868,3564693,3564136,3564107,3564786,3564107,3564868,3564709,3564136,3564107,3564786,3564107,3564868,3565021,3564136,3564107,3564786,3564107,3564988,3564136,3564115,3564786,3564115,3564988,3564136,3564115,3564115,3564988,3564144,3564673,3564988,3564144,3564673,3564988,3564144,3564673,3564988,3564144,3564673,3564144,3564673,3564144,3564673,3564144,3564673,3564144,3564673,3564144,3564673,3564144,3564673,3564144,3564673,3564144,3564673,3564144,3564673,3564144,3564673,3564673,3564673,3564673</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L12 W13/25; N=114; EHP=4094.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x2,normal:17x14,normal:18x14,fast:30x3,heavy:31x2,heavy:40x1,fast:58x3,fast:64x3,heavy:67x1,heavy:70x1,heavy:80x2,medium:83x5,swarm:84x31,heavy:86x2,heavy:88x1,fast:98x4,medium:108x6,medium:123x6,heavy:127x1</t>
+          <t>L12 W13/25; N=114; EHP=9377.012696; air:2x6,air:11x6,air:12x6,air:13x6,air:14x4,fast:30x3,fast:58x3,fast:64x3,fast:98x4,heavy:31x2,heavy:40x1,heavy:67x1,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x1,heavy:127x1,medium:83x5,medium:108x6,medium:123x6,normal:17x14,normal:18x14,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>3566136,3566673,3566242,3566019,3566668,3566253,3566136,3566673,3566242,3566019,3566668,3566253,3566136,3566673,3566242,3566019,3566668,3566325,3566136,3566673,3566466,3566091,3566668,3566325,3566136,3566673,3566466,3566091,3566668,3566541,3566136,3566673,3566466,3566091,3566668,3566565,3566136,3566673,3566466,3566099,3566868,3566645,3566136,3566673,3566514,3566099,3566868,3566693,3566136,3566673,3566514,3566107,3566868,3566693,3566136,3566673,3566514,3566107,3566868,3566709,3566136,3566673,3566514,3566107,3566868,3567021,3566136,3566673,3566786,3566115,3566868,3567021,3566136,3566673,3566786,3566115,3566988,3566136,3566673,3566786,3566115,3566988,3566144,3566673,3566988,3566144,3566673,3566988,3566144,3566673,3566988,3566144,3566673,3566988,3566144,3566673,3566144,3566673,3566144,3566673,3566144,3566673,3566144,3566673,3566144,3566673,3566144,3566673,3566144,3566673,3566144,3566673,3566144,3566673,3566144,3566673,3566673,3566673,3566673,3566673</t>
+          <t>3566136,3566019,3566242,3566019,3566668,3566253,3566136,3566019,3566242,3566019,3566668,3566253,3566136,3566019,3566242,3566019,3566668,3566325,3566136,3566091,3566466,3566091,3566668,3566325,3566136,3566091,3566466,3566091,3566668,3566541,3566136,3566091,3566466,3566091,3566668,3566565,3566136,3566099,3566466,3566099,3566868,3566645,3566136,3566099,3566514,3566099,3566868,3566693,3566136,3566107,3566514,3566107,3566868,3566693,3566136,3566107,3566514,3566107,3566868,3566709,3566136,3566107,3566514,3566107,3566868,3567021,3566136,3566115,3566786,3566115,3566868,3567021,3566136,3566115,3566786,3566115,3566988,3566136,3566115,3566786,3566115,3566988,3566144,3566673,3566988,3566144,3566673,3566988,3566144,3566673,3566988,3566144,3566673,3566988,3566144,3566673,3566144,3566673,3566144,3566673,3566144,3566673,3566144,3566673,3566144,3566673,3566144,3566673,3566144,3566673,3566144,3566673,3566144,3566673,3566144,3566673,3566673,3566673,3566673,3566673</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L12 W14/25; N=120; EHP=4940.000000; air:2x3,air:11x3,air:12x2,air:13x3,air:14x3,normal:17x14,normal:18x15,fast:30x3,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,heavy:67x1,heavy:70x1,heavy:80x1,medium:83x6,swarm:84x33,heavy:86x2,heavy:88x1,fast:98x3,medium:108x6,medium:123x6,heavy:127x2</t>
+          <t>L12 W14/25; N=120; EHP=11307.308311; air:2x6,air:11x6,air:12x4,air:13x6,air:14x6,fast:30x3,fast:58x4,fast:64x4,fast:98x3,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x1,heavy:80x1,heavy:86x2,heavy:88x1,heavy:127x2,medium:83x6,medium:108x6,medium:123x6,normal:17x14,normal:18x15,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>3568136,3568673,3568242,3568019,3568668,3568253,3568542,3568136,3568673,3568242,3568019,3568668,3568253,3568136,3568673,3568242,3568019,3568668,3568325,3568136,3568673,3568242,3568091,3568668,3568325,3568136,3568673,3568466,3568091,3568668,3568541,3568136,3568673,3568466,3568091,3568668,3568565,3568136,3568673,3568466,3568099,3568868,3568565,3568136,3568673,3568514,3568099,3568868,3568645,3568136,3568673,3568514,3568099,3568868,3568693,3568136,3568673,3568514,3568107,3568868,3568709,3568136,3568673,3568514,3568107,3568868,3569021,3568136,3568673,3568786,3568107,3568868,3569021,3568136,3568673,3568786,3568115,3568988,3568136,3568673,3568786,3568115,3568988,3568136,3568673,3568786,3568115,3568988,3568144,3568673,3568988,3568144,3568673,3568988,3568144,3568673,3568988,3568144,3568673,3568144,3568673,3568144,3568673,3568144,3568673,3568144,3568673,3568144,3568673,3568144,3568673,3568144,3568673,3568144,3568673,3568144,3568673,3568144,3568673,3568144,3568673,3568673,3568673,3568673,3568673,3568673</t>
+          <t>3568136,3568019,3568242,3568019,3568668,3568253,3568542,3568136,3568019,3568242,3568019,3568668,3568253,3568136,3568019,3568242,3568019,3568668,3568325,3568136,3568091,3568242,3568091,3568668,3568325,3568136,3568091,3568466,3568091,3568668,3568541,3568136,3568091,3568466,3568091,3568668,3568565,3568136,3568099,3568466,3568099,3568868,3568565,3568136,3568099,3568514,3568099,3568868,3568645,3568136,3568099,3568514,3568099,3568868,3568693,3568136,3568107,3568514,3568107,3568868,3568709,3568136,3568107,3568514,3568107,3568868,3569021,3568136,3568107,3568786,3568107,3568868,3569021,3568136,3568115,3568786,3568115,3568988,3568136,3568115,3568786,3568115,3568988,3568136,3568115,3568786,3568115,3568988,3568144,3568673,3568988,3568144,3568673,3568988,3568144,3568673,3568988,3568144,3568673,3568144,3568673,3568144,3568673,3568144,3568673,3568144,3568673,3568144,3568673,3568144,3568673,3568144,3568673,3568144,3568673,3568144,3568673,3568144,3568673,3568144,3568673,3568673,3568673,3568673,3568673,3568673</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L12 W15/25; N=126; EHP=8622.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x15,normal:18x15,fast:30x4,heavy:31x2,heavy:40x2,fast:58x3,fast:64x4,elite:67x1,heavy:67x1,heavy:70x2,heavy:80x1,medium:83x6,swarm:84x35,heavy:86x1,heavy:88x1,fast:98x4,medium:108x6,medium:123x6,heavy:127x2</t>
+          <t>L12 W15/25; N=126; EHP=19736.076996; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,elite:67x1,fast:30x4,fast:58x3,fast:64x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x1,heavy:127x2,medium:83x6,medium:108x6,medium:123x6,normal:17x15,normal:18x15,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>3570136,3570673,3570242,3570019,3570668,3570253,3570136,3570673,3570242,3570019,3570668,3570325,3570136,3570673,3570242,3570019,3570668,3570325,3570136,3570673,3570242,3570091,3570668,3570541,3570136,3570673,3570466,3570091,3570668,3570541,3570136,3570673,3570466,3570091,3570668,3570565,3570136,3570673,3570466,3570091,3570868,3570565,3570136,3570673,3570466,3570099,3570868,3570645,3570136,3570673,3570514,3570099,3570868,3570693,3570136,3570673,3570514,3570099,3570868,3570709,3570136,3570673,3570514,3570107,3570868,3570709,3570136,3570673,3570786,3570107,3570868,3571021,3570136,3570673,3570786,3570107,3570988,3571021,3570136,3570673,3570786,3570115,3570988,3570136,3570673,3570786,3570115,3570988,3570136,3570673,3570115,3570988,3570144,3570673,3570988,3570144,3570673,3570988,3570144,3570673,3570988,3570144,3570673,3570144,3570673,3570144,3570673,3570144,3570673,3570144,3570673,3570144,3570673,3570144,3570673,3570144,3570673,3570144,3570673,3570144,3570673,3570144,3570673,3570144,3570673,3570144,3570673,3570144,3570673,3570673,3570673,3570673</t>
+          <t>3570136,3570019,3570242,3570019,3570668,3570253,3570136,3570019,3570242,3570019,3570668,3570325,3570136,3570019,3570242,3570019,3570668,3570325,3570136,3570091,3570242,3570091,3570668,3570541,3570136,3570091,3570466,3570091,3570668,3570541,3570136,3570091,3570466,3570091,3570668,3570565,3570136,3570091,3570466,3570091,3570868,3570565,3570136,3570099,3570466,3570099,3570868,3570645,3570136,3570099,3570514,3570099,3570868,3570693,3570136,3570099,3570514,3570099,3570868,3570709,3570136,3570107,3570514,3570107,3570868,3570709,3570136,3570107,3570786,3570107,3570868,3571021,3570136,3570107,3570786,3570107,3570988,3571021,3570136,3570115,3570786,3570115,3570988,3570136,3570115,3570786,3570115,3570988,3570136,3570115,3570115,3570988,3570144,3570673,3570988,3570144,3570673,3570988,3570144,3570673,3570988,3570144,3570673,3570144,3570673,3570144,3570673,3570144,3570673,3570144,3570673,3570144,3570673,3570144,3570673,3570144,3570673,3570144,3570673,3570144,3570673,3570144,3570673,3570144,3570673,3570144,3570673,3570144,3570673,3570673,3570673,3570673</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L12 W16/25; N=132; EHP=8795.000000; air:2x3,air:11x4,air:12x3,air:13x3,air:14x3,normal:17x16,normal:18x17,fast:30x4,heavy:31x1,heavy:40x2,fast:58x4,fast:64x3,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x6,swarm:84x36,heavy:86x1,heavy:88x2,fast:98x4,medium:108x6,medium:123x7,heavy:127x2</t>
+          <t>L12 W16/25; N=132; EHP=20141.392068; air:2x6,air:11x8,air:12x6,air:13x6,air:14x6,fast:30x4,fast:58x4,fast:64x3,fast:98x4,heavy:31x1,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x2,heavy:127x2,medium:83x6,medium:108x6,medium:123x7,normal:17x16,normal:18x17,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>3572136,3572673,3572242,3572019,3572668,3572253,3572136,3572673,3572242,3572019,3572668,3572325,3572136,3572673,3572242,3572019,3572668,3572541,3572136,3572673,3572242,3572091,3572668,3572541,3572136,3572673,3572466,3572091,3572668,3572565,3572136,3572673,3572466,3572091,3572668,3572565,3572136,3572673,3572466,3572099,3572668,3572645,3572136,3572673,3572466,3572099,3572868,3572645,3572136,3572673,3572514,3572099,3572868,3572693,3572136,3572673,3572514,3572099,3572868,3572709,3572136,3572673,3572514,3572107,3572868,3572709,3572136,3572673,3572514,3572107,3572868,3573021,3572136,3572673,3572786,3572107,3572868,3573021,3572136,3572673,3572786,3572115,3572868,3572136,3572673,3572786,3572115,3572988,3572136,3572673,3572786,3572115,3572988,3572136,3572673,3572115,3572988,3572144,3572673,3572988,3572144,3572673,3572988,3572144,3572673,3572988,3572144,3572673,3572144,3572673,3572144,3572673,3572144,3572673,3572144,3572673,3572144,3572673,3572144,3572673,3572144,3572673,3572144,3572673,3572144,3572673,3572144,3572673,3572144,3572673,3572144,3572673,3572144,3572673,3572673,3572673,3572673,3572673</t>
+          <t>3572136,3572019,3572242,3572019,3572668,3572253,3572136,3572019,3572242,3572019,3572668,3572325,3572136,3572019,3572242,3572019,3572668,3572541,3572136,3572091,3572242,3572091,3572668,3572541,3572136,3572091,3572466,3572091,3572668,3572565,3572136,3572091,3572466,3572091,3572668,3572565,3572136,3572099,3572466,3572099,3572668,3572645,3572136,3572099,3572466,3572099,3572868,3572645,3572136,3572099,3572514,3572099,3572868,3572693,3572136,3572099,3572514,3572099,3572868,3572709,3572136,3572107,3572514,3572107,3572868,3572709,3572136,3572107,3572514,3572107,3572868,3573021,3572136,3572107,3572786,3572107,3572868,3573021,3572136,3572115,3572786,3572115,3572868,3572136,3572115,3572786,3572115,3572988,3572136,3572115,3572786,3572115,3572988,3572136,3572115,3572115,3572988,3572144,3572673,3572988,3572144,3572673,3572988,3572144,3572673,3572988,3572144,3572673,3572144,3572673,3572144,3572673,3572144,3572673,3572144,3572673,3572144,3572673,3572144,3572673,3572144,3572673,3572144,3572673,3572144,3572673,3572144,3572673,3572144,3572673,3572144,3572673,3572144,3572673,3572673,3572673,3572673,3572673</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L12 W17/25; N=138; EHP=8971.000000; air:2x3,air:11x3,air:12x4,air:13x3,air:14x4,normal:17x17,normal:18x17,fast:30x4,heavy:31x1,heavy:40x1,fast:58x4,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x38,heavy:86x1,heavy:88x2,fast:98x4,medium:108x7,medium:123x6,heavy:127x2</t>
+          <t>L12 W17/25; N=138; EHP=20549.893029; air:2x6,air:11x6,air:12x8,air:13x6,air:14x8,fast:30x4,fast:58x4,fast:64x4,fast:98x4,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x1,heavy:88x2,heavy:127x2,medium:83x7,medium:108x7,medium:123x6,normal:17x17,normal:18x17,swarm:84x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>3574136,3574673,3574242,3574019,3574668,3574253,3574136,3574673,3574242,3574019,3574668,3574253,3574136,3574673,3574242,3574019,3574668,3574325,3574136,3574673,3574242,3574019,3574668,3574541,3574136,3574673,3574466,3574091,3574668,3574541,3574136,3574673,3574466,3574091,3574668,3574565,3574136,3574673,3574466,3574091,3574668,3574565,3574136,3574673,3574466,3574099,3574868,3574645,3574136,3574673,3574466,3574099,3574868,3574645,3574136,3574673,3574514,3574099,3574868,3574693,3574136,3574673,3574514,3574099,3574868,3574693,3574136,3574673,3574514,3574107,3574868,3574709,3574136,3574673,3574514,3574107,3574868,3574709,3574136,3574673,3574786,3574107,3574868,3575021,3574136,3574673,3574786,3574115,3574988,3574136,3574673,3574786,3574115,3574988,3574136,3574673,3574786,3574115,3574988,3574144,3574673,3574988,3574144,3574673,3574988,3574144,3574673,3574988,3574144,3574673,3574988,3574144,3574673,3574144,3574673,3574144,3574673,3574144,3574673,3574144,3574673,3574144,3574673,3574144,3574673,3574144,3574673,3574144,3574673,3574144,3574673,3574144,3574673,3574144,3574673,3574144,3574673,3574144,3574673,3574673,3574673,3574673,3574673,3574673</t>
+          <t>3574136,3574019,3574242,3574019,3574668,3574253,3574136,3574019,3574242,3574019,3574668,3574253,3574136,3574019,3574242,3574019,3574668,3574325,3574136,3574019,3574242,3574019,3574668,3574541,3574136,3574091,3574466,3574091,3574668,3574541,3574136,3574091,3574466,3574091,3574668,3574565,3574136,3574091,3574466,3574091,3574668,3574565,3574136,3574099,3574466,3574099,3574868,3574645,3574136,3574099,3574466,3574099,3574868,3574645,3574136,3574099,3574514,3574099,3574868,3574693,3574136,3574099,3574514,3574099,3574868,3574693,3574136,3574107,3574514,3574107,3574868,3574709,3574136,3574107,3574514,3574107,3574868,3574709,3574136,3574107,3574786,3574107,3574868,3575021,3574136,3574115,3574786,3574115,3574988,3574136,3574115,3574786,3574115,3574988,3574136,3574115,3574786,3574115,3574988,3574144,3574673,3574988,3574144,3574673,3574988,3574144,3574673,3574988,3574144,3574673,3574988,3574144,3574673,3574144,3574673,3574144,3574673,3574144,3574673,3574144,3574673,3574144,3574673,3574144,3574673,3574144,3574673,3574144,3574673,3574144,3574673,3574144,3574673,3574144,3574673,3574144,3574673,3574144,3574673,3574673,3574673,3574673,3574673,3574673</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L12 W18/25; N=144; EHP=9586.000000; air:2x4,air:11x3,air:12x4,air:13x3,air:14x3,normal:17x17,normal:18x18,fast:30x4,heavy:31x2,heavy:40x1,fast:58x5,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x40,heavy:86x2,heavy:88x2,fast:98x4,medium:108x7,medium:123x7,heavy:127x1</t>
+          <t>L12 W18/25; N=144; EHP=21946.479708; air:2x8,air:11x6,air:12x8,air:13x6,air:14x6,fast:30x4,fast:58x5,fast:64x4,fast:98x4,heavy:31x2,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x7,medium:108x7,medium:123x7,normal:17x17,normal:18x18,swarm:84x23 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>3576136,3576673,3576242,3576019,3576668,3576253,3576136,3576673,3576242,3576019,3576668,3576253,3576136,3576673,3576242,3576019,3576668,3576325,3576136,3576673,3576242,3576019,3576668,3576325,3576136,3576673,3576242,3576091,3576668,3576541,3576136,3576673,3576466,3576091,3576668,3576541,3576136,3576673,3576466,3576091,3576668,3576565,3576136,3576673,3576466,3576091,3576868,3576645,3576136,3576673,3576466,3576099,3576868,3576645,3576136,3576673,3576514,3576099,3576868,3576693,3576136,3576673,3576514,3576099,3576868,3576693,3576136,3576673,3576514,3576107,3576868,3576709,3576136,3576673,3576514,3576107,3576868,3576709,3576136,3576673,3576514,3576107,3576868,3577021,3576136,3576673,3576786,3576107,3576988,3577021,3576136,3576673,3576786,3576115,3576988,3576136,3576673,3576786,3576115,3576988,3576136,3576673,3576786,3576115,3576988,3576144,3576673,3576988,3576144,3576673,3576988,3576144,3576673,3576988,3576144,3576673,3576988,3576144,3576673,3576144,3576673,3576144,3576673,3576144,3576673,3576144,3576673,3576144,3576673,3576144,3576673,3576144,3576673,3576144,3576673,3576144,3576673,3576144,3576673,3576144,3576673,3576144,3576673,3576673,3576673,3576673,3576673,3576673,3576673,3576673</t>
+          <t>3576136,3576019,3576242,3576019,3576668,3576253,3576136,3576019,3576242,3576019,3576668,3576253,3576136,3576019,3576242,3576019,3576668,3576325,3576136,3576019,3576242,3576019,3576668,3576325,3576136,3576091,3576242,3576091,3576668,3576541,3576136,3576091,3576466,3576091,3576668,3576541,3576136,3576091,3576466,3576091,3576668,3576565,3576136,3576091,3576466,3576091,3576868,3576645,3576136,3576099,3576466,3576099,3576868,3576645,3576136,3576099,3576514,3576099,3576868,3576693,3576136,3576099,3576514,3576099,3576868,3576693,3576136,3576107,3576514,3576107,3576868,3576709,3576136,3576107,3576514,3576107,3576868,3576709,3576136,3576107,3576514,3576107,3576868,3577021,3576136,3576107,3576786,3576107,3576988,3577021,3576136,3576115,3576786,3576115,3576988,3576136,3576115,3576786,3576115,3576988,3576136,3576115,3576786,3576115,3576988,3576144,3576673,3576988,3576144,3576673,3576988,3576144,3576673,3576988,3576144,3576673,3576988,3576144,3576673,3576144,3576673,3576144,3576673,3576144,3576673,3576144,3576673,3576144,3576673,3576144,3576673,3576144,3576673,3576144,3576673,3576144,3576673,3576144,3576673,3576144,3576673,3576144,3576673,3576673,3576673,3576673,3576673,3576673,3576673,3576673</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L12 W19/25; N=150; EHP=11102.000000; air:2x4,air:11x4,air:12x3,air:13x4,air:14x3,normal:17x18,normal:18x17,fast:30x5,heavy:31x2,heavy:40x2,fast:58x4,fast:64x5,heavy:67x2,heavy:70x1,heavy:80x2,medium:83x7,swarm:84x42,heavy:86x2,heavy:88x2,fast:98x4,medium:108x7,medium:123x8,heavy:127x2</t>
+          <t>L12 W19/25; N=150; EHP=25421.464060; air:2x8,air:11x8,air:12x6,air:13x8,air:14x6,fast:30x5,fast:58x4,fast:64x5,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x7,medium:108x7,medium:123x8,normal:17x18,normal:18x17,swarm:84x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>3578136,3578673,3578242,3578019,3578668,3578253,3578542,3578136,3578673,3578242,3578019,3578668,3578253,3578136,3578673,3578242,3578019,3578668,3578325,3578136,3578673,3578242,3578091,3578668,3578325,3578136,3578673,3578242,3578091,3578668,3578541,3578136,3578673,3578466,3578091,3578668,3578565,3578136,3578673,3578466,3578091,3578668,3578565,3578136,3578673,3578466,3578099,3578668,3578645,3578136,3578673,3578466,3578099,3578868,3578645,3578136,3578673,3578514,3578099,3578868,3578693,3578136,3578673,3578514,3578099,3578868,3578693,3578136,3578673,3578514,3578107,3578868,3578709,3578136,3578673,3578514,3578107,3578868,3578709,3578136,3578673,3578786,3578107,3578868,3579021,3578136,3578673,3578786,3578107,3578868,3579021,3578136,3578673,3578786,3578115,3578868,3578136,3578673,3578786,3578115,3578988,3578136,3578673,3578786,3578115,3578988,3578144,3578673,3578115,3578988,3578144,3578673,3578988,3578144,3578673,3578988,3578144,3578673,3578988,3578144,3578673,3578988,3578144,3578673,3578144,3578673,3578144,3578673,3578144,3578673,3578144,3578673,3578144,3578673,3578144,3578673,3578144,3578673,3578144,3578673,3578144,3578673,3578144,3578673,3578144,3578673,3578144,3578673,3578144,3578673,3578673,3578673,3578673,3578673,3578673,3578673</t>
+          <t>3578136,3578019,3578242,3578019,3578668,3578253,3578542,3578136,3578019,3578242,3578019,3578668,3578253,3578136,3578019,3578242,3578019,3578668,3578325,3578136,3578091,3578242,3578091,3578668,3578325,3578136,3578091,3578242,3578091,3578668,3578541,3578136,3578091,3578466,3578091,3578668,3578565,3578136,3578091,3578466,3578091,3578668,3578565,3578136,3578099,3578466,3578099,3578668,3578645,3578136,3578099,3578466,3578099,3578868,3578645,3578136,3578099,3578514,3578099,3578868,3578693,3578136,3578099,3578514,3578099,3578868,3578693,3578136,3578107,3578514,3578107,3578868,3578709,3578136,3578107,3578514,3578107,3578868,3578709,3578136,3578107,3578786,3578107,3578868,3579021,3578136,3578107,3578786,3578107,3578868,3579021,3578136,3578115,3578786,3578115,3578868,3578136,3578115,3578786,3578115,3578988,3578136,3578115,3578786,3578115,3578988,3578144,3578115,3578115,3578988,3578144,3578673,3578988,3578144,3578673,3578988,3578144,3578673,3578988,3578144,3578673,3578988,3578144,3578673,3578144,3578673,3578144,3578673,3578144,3578673,3578144,3578673,3578144,3578673,3578144,3578673,3578144,3578673,3578144,3578673,3578144,3578673,3578144,3578673,3578144,3578673,3578144,3578673,3578144,3578673,3578673,3578673,3578673,3578673,3578673,3578673</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L12 W20/25; N=156; EHP=18643.000000; air:2x3,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x18,normal:18x19,fast:30x5,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,elite:67x1,heavy:67x1,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x43,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x7,heavy:127x2</t>
+          <t>L12 W20/25; N=156; EHP=42686.192062; air:2x6,air:11x8,air:12x8,air:13x8,air:14x8,elite:67x1,fast:30x5,fast:58x4,fast:64x4,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x7,normal:17x18,normal:18x19,swarm:84x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>10017605,10017615,10017607,10048580,10017614,10017608,10017605,10017615,10017607,10048580,10017614,10017608,10017605,10017615,10017607,10048580,10017614,10017609,10017605,10017615,10017607,10048580,10017614,10017609,10017605,10017615,10017610,10017602,10017614,10045170,10017605,10017615,10017610,10017602,10017614,10045170,10017605,10017615,10017610,10017602,10017614,10017612,10017605,10017615,10017610,10017602,10017614,10017612,10017605,10017615,10017610,10048581,10017618,10017613,10017605,10017615,10017611,10048581,10017618,10017613,10017605,10017615,10017611,10048581,10017618,10017616,10017605,10017615,10017611,10048581,10017618,10017616,10017605,10017615,10017611,10017603,10017618,10045171,10017605,10017615,10017611,10017603,10017618,10045171,10017605,10017615,10017617,10017603,10017618,10017620,10017605,10017615,10017617,10017604,10017618,10017620,10017605,10017615,10017617,10017604,10017619,10017605,10017615,10017617,10017604,10017619,10017605,10017615,10017617,10017604,10017619,10017605,10017615,10017619,10017606,10017615,10017619,10017606,10017615,10017619,10017606,10017615,10017619,10017606,10017615,10017619,10017606,10017615,10017606,10017615,10017606,10017615,10017606,10017615,10017606,10017615,10017606,10017615,10017606,10017615,10017606,10017615,10017606,10017615,10017606,10017615,10017606,10017615,10017606,10017615,10017606,10017615,10017606,10017615,10017606,10017615,10017615,10017615,10017615,10017615,10017615,10017615</t>
+          <t>10017605,10048580,10017607,10048580,10017614,10017608,10017605,10048580,10017607,10048580,10017614,10017608,10017605,10048580,10017607,10048580,10017614,10017609,10017605,10048580,10017607,10048580,10017614,10017609,10017605,10017602,10017610,10017602,10017614,10045170,10017605,10017602,10017610,10017602,10017614,10045170,10017605,10017602,10017610,10017602,10017614,10017612,10017605,10017602,10017610,10017602,10017614,10017612,10017605,10048581,10017610,10048581,10017618,10017613,10017605,10048581,10017611,10048581,10017618,10017613,10017605,10048581,10017611,10048581,10017618,10017616,10017605,10048581,10017611,10048581,10017618,10017616,10017605,10017603,10017611,10017603,10017618,10045171,10017605,10017603,10017611,10017603,10017618,10045171,10017605,10017603,10017617,10017603,10017618,10017620,10017605,10017604,10017617,10017604,10017618,10017620,10017605,10017604,10017617,10017604,10017619,10017605,10017604,10017617,10017604,10017619,10017605,10017604,10017617,10017604,10017619,10017605,10017615,10017619,10017606,10017615,10017619,10017606,10017615,10017619,10017606,10017615,10017619,10017606,10017615,10017619,10017606,10017615,10017606,10017615,10017606,10017615,10017606,10017615,10017606,10017615,10017606,10017615,10017606,10017615,10017606,10017615,10017606,10017615,10017606,10017615,10017606,10017615,10017606,10017615,10017606,10017615,10017606,10017615,10017606,10017615,10017615,10017615,10017615,10017615,10017615,10017615</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L12 W21/25; N=162; EHP=19016.000000; air:2x4,air:11x4,air:12x4,air:13x3,air:14x4,normal:17x20,normal:18x19,fast:30x4,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x45,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L12 W21/25; N=162; EHP=43530.741444; air:2x8,air:11x8,air:12x8,air:13x6,air:14x8,fast:30x4,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x8,normal:17x20,normal:18x19,swarm:84x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>10017624,10017634,10017626,10048582,10017633,10017627,10017624,10017634,10017626,10048582,10017633,10017627,10017624,10017634,10017626,10048582,10017633,10017628,10017624,10017634,10017626,10048582,10017633,10017628,10017624,10017634,10017626,10017621,10017633,10017631,10017624,10017634,10017629,10017621,10017633,10017631,10017624,10017634,10017629,10017621,10017633,10017632,10017624,10017634,10017629,10017621,10017633,10017632,10017624,10017634,10017629,10048583,10017638,10045172,10017624,10017634,10017629,10048583,10017638,10045172,10017624,10017634,10017630,10048583,10017638,10017635,10017624,10017634,10017630,10048583,10017638,10017635,10017624,10017634,10017630,10017622,10017638,10017636,10017624,10017634,10017630,10017622,10017638,10017636,10017624,10017634,10017630,10017622,10017638,10017640,10017624,10017634,10017637,10017622,10017638,10017640,10017624,10017634,10017637,10017623,10017639,10017624,10017634,10017637,10017623,10017639,10017624,10017634,10017637,10017623,10017639,10017624,10017634,10017637,10017623,10017639,10017625,10017634,10017639,10017625,10017634,10017639,10017625,10017634,10017639,10017625,10017634,10017639,10017625,10017634,10017639,10017625,10017634,10017625,10017634,10017625,10017634,10017625,10017634,10017625,10017634,10017625,10017634,10017625,10017634,10017625,10017634,10017625,10017634,10017625,10017634,10017625,10017634,10017625,10017634,10017625,10017634,10017625,10017634,10017625,10017634,10017634,10017634,10017634,10017634,10017634,10017634,10017634</t>
+          <t>10017624,10048582,10017626,10048582,10017633,10017627,10017624,10048582,10017626,10048582,10017633,10017627,10017624,10048582,10017626,10048582,10017633,10017628,10017624,10048582,10017626,10048582,10017633,10017628,10017624,10017621,10017626,10017621,10017633,10017631,10017624,10017621,10017629,10017621,10017633,10017631,10017624,10017621,10017629,10017621,10017633,10017632,10017624,10017621,10017629,10017621,10017633,10017632,10017624,10048583,10017629,10048583,10017638,10045172,10017624,10048583,10017629,10048583,10017638,10045172,10017624,10048583,10017630,10048583,10017638,10017635,10017624,10048583,10017630,10048583,10017638,10017635,10017624,10017622,10017630,10017622,10017638,10017636,10017624,10017622,10017630,10017622,10017638,10017636,10017624,10017622,10017630,10017622,10017638,10017640,10017624,10017622,10017637,10017622,10017638,10017640,10017624,10017623,10017637,10017623,10017639,10017624,10017623,10017637,10017623,10017639,10017624,10017623,10017637,10017623,10017639,10017624,10017623,10017637,10017623,10017639,10017625,10017634,10017639,10017625,10017634,10017639,10017625,10017634,10017639,10017625,10017634,10017639,10017625,10017634,10017639,10017625,10017634,10017625,10017634,10017625,10017634,10017625,10017634,10017625,10017634,10017625,10017634,10017625,10017634,10017625,10017634,10017625,10017634,10017625,10017634,10017625,10017634,10017625,10017634,10017625,10017634,10017625,10017634,10017625,10017634,10017634,10017634,10017634,10017634,10017634,10017634,10017634</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L12 W22/25; N=168; EHP=19397.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x20,normal:18x20,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x47,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x9,heavy:127x2</t>
+          <t>L12 W22/25; N=168; EHP=44413.092402; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x5,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x9,normal:17x20,normal:18x20,swarm:84x27 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>10017644,10017655,10017646,10048584,10017654,10017647,10017644,10017655,10017646,10048584,10017654,10017647,10017644,10017655,10017646,10048584,10017654,10017647,10017644,10017655,10017646,10048584,10017654,10017648,10017644,10017655,10017646,10017641,10017654,10017648,10017644,10017655,10017649,10017641,10017654,10017651,10017644,10017655,10017649,10017641,10017654,10017651,10017644,10017655,10017649,10017641,10017654,10017652,10017644,10017655,10017649,10048585,10017654,10017652,10017644,10017655,10017649,10048585,10017658,10017653,10017644,10017655,10017650,10048585,10017658,10017653,10017644,10017655,10017650,10048585,10017658,10045173,10017644,10017655,10017650,10048585,10017658,10045173,10017644,10017655,10017650,10017642,10017658,10017656,10017644,10017655,10017650,10017642,10017658,10017656,10017644,10017655,10017657,10017642,10017658,10017660,10017644,10017655,10017657,10017642,10017658,10017660,10017644,10017655,10017657,10017643,10017658,10017644,10017655,10017657,10017643,10017659,10017644,10017655,10017657,10017643,10017659,10017644,10017655,10017643,10017659,10017645,10017655,10017659,10017645,10017655,10017659,10017645,10017655,10017659,10017645,10017655,10017659,10017645,10017655,10017659,10017645,10017655,10017645,10017655,10017645,10017655,10017645,10017655,10017645,10017655,10017645,10017655,10017645,10017655,10017645,10017655,10017645,10017655,10017645,10017655,10017645,10017655,10017645,10017655,10017645,10017655,10017645,10017655,10017645,10017655,10017645,10017655,10017655,10017655,10017655,10017655,10017655,10017655</t>
+          <t>10017644,10048584,10017646,10048584,10017654,10017647,10017644,10048584,10017646,10048584,10017654,10017647,10017644,10048584,10017646,10048584,10017654,10017647,10017644,10048584,10017646,10048584,10017654,10017648,10017644,10017641,10017646,10017641,10017654,10017648,10017644,10017641,10017649,10017641,10017654,10017651,10017644,10017641,10017649,10017641,10017654,10017651,10017644,10017641,10017649,10017641,10017654,10017652,10017644,10048585,10017649,10048585,10017654,10017652,10017644,10048585,10017649,10048585,10017658,10017653,10017644,10048585,10017650,10048585,10017658,10017653,10017644,10048585,10017650,10048585,10017658,10045173,10017644,10048585,10017650,10048585,10017658,10045173,10017644,10017642,10017650,10017642,10017658,10017656,10017644,10017642,10017650,10017642,10017658,10017656,10017644,10017642,10017657,10017642,10017658,10017660,10017644,10017642,10017657,10017642,10017658,10017660,10017644,10017643,10017657,10017643,10017658,10017644,10017643,10017657,10017643,10017659,10017644,10017643,10017657,10017643,10017659,10017644,10017643,10017643,10017659,10017645,10017655,10017659,10017645,10017655,10017659,10017645,10017655,10017659,10017645,10017655,10017659,10017645,10017655,10017659,10017645,10017655,10017645,10017655,10017645,10017655,10017645,10017655,10017645,10017655,10017645,10017655,10017645,10017655,10017645,10017655,10017645,10017655,10017645,10017655,10017645,10017655,10017645,10017655,10017645,10017655,10017645,10017655,10017645,10017655,10017645,10017655,10017655,10017655,10017655,10017655,10017655,10017655</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L12 W23/25; N=174; EHP=19785.000000; air:2x4,air:11x4,air:12x5,air:13x4,air:14x4,normal:17x21,normal:18x21,fast:30x5,heavy:31x3,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x48,heavy:86x2,heavy:88x2,fast:98x5,medium:108x9,medium:123x8,heavy:127x2</t>
+          <t>L12 W23/25; N=174; EHP=45306.348607; air:2x8,air:11x8,air:12x10,air:13x8,air:14x8,fast:30x5,fast:58x5,fast:64x5,fast:98x5,heavy:31x3,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x9,medium:108x9,medium:123x8,normal:17x21,normal:18x21,swarm:84x27 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>10017664,10017674,10017666,10048586,10017673,10045174,10017664,10017674,10017666,10048586,10017673,10045174,10017664,10017674,10017666,10048586,10017673,10017667,10017664,10017674,10017666,10048586,10017673,10017667,10017664,10017674,10017666,10048586,10017673,10017667,10017664,10017674,10017666,10017661,10017673,10017670,10017664,10017674,10017668,10017661,10017673,10017670,10017664,10017674,10017668,10017661,10017673,10017671,10017664,10017674,10017668,10017661,10017673,10017671,10017664,10017674,10017668,10048587,10017678,10017672,10017664,10017674,10017668,10048587,10017678,10017672,10017664,10017674,10017669,10048587,10017678,10017675,10017664,10017674,10017669,10048587,10017678,10017675,10017664,10017674,10017669,10017662,10017678,10017676,10017664,10017674,10017669,10017662,10017678,10017676,10017664,10017674,10017669,10017662,10017678,10017680,10017664,10017674,10017677,10017662,10017678,10017680,10017664,10017674,10017677,10017662,10017678,10017680,10017664,10017674,10017677,10017663,10017679,10017664,10017674,10017677,10017663,10017679,10017664,10017674,10017677,10017663,10017679,10017665,10017674,10017663,10017679,10017665,10017674,10017679,10017665,10017674,10017679,10017665,10017674,10017679,10017665,10017674,10017679,10017665,10017674,10017679,10017665,10017674,10017665,10017674,10017665,10017674,10017665,10017674,10017665,10017674,10017665,10017674,10017665,10017674,10017665,10017674,10017665,10017674,10017665,10017674,10017665,10017674,10017665,10017674,10017665,10017674,10017665,10017674,10017665,10017674,10017674,10017674,10017674,10017674,10017674,10017674,10017674,10017674</t>
+          <t>10017664,10048586,10017666,10048586,10017673,10045174,10017664,10048586,10017666,10048586,10017673,10045174,10017664,10048586,10017666,10048586,10017673,10017667,10017664,10048586,10017666,10048586,10017673,10017667,10017664,10048586,10017666,10048586,10017673,10017667,10017664,10017661,10017666,10017661,10017673,10017670,10017664,10017661,10017668,10017661,10017673,10017670,10017664,10017661,10017668,10017661,10017673,10017671,10017664,10017661,10017668,10017661,10017673,10017671,10017664,10048587,10017668,10048587,10017678,10017672,10017664,10048587,10017668,10048587,10017678,10017672,10017664,10048587,10017669,10048587,10017678,10017675,10017664,10048587,10017669,10048587,10017678,10017675,10017664,10017662,10017669,10017662,10017678,10017676,10017664,10017662,10017669,10017662,10017678,10017676,10017664,10017662,10017669,10017662,10017678,10017680,10017664,10017662,10017677,10017662,10017678,10017680,10017664,10017662,10017677,10017662,10017678,10017680,10017664,10017663,10017677,10017663,10017679,10017664,10017663,10017677,10017663,10017679,10017664,10017663,10017677,10017663,10017679,10017665,10017663,10017663,10017679,10017665,10017674,10017679,10017665,10017674,10017679,10017665,10017674,10017679,10017665,10017674,10017679,10017665,10017674,10017679,10017665,10017674,10017665,10017674,10017665,10017674,10017665,10017674,10017665,10017674,10017665,10017674,10017665,10017674,10017665,10017674,10017665,10017674,10017665,10017674,10017665,10017674,10017665,10017674,10017665,10017674,10017665,10017674,10017665,10017674,10017674,10017674,10017674,10017674,10017674,10017674,10017674,10017674</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L12 W24/25; N=180; EHP=21186.000000; air:2x5,air:11x4,air:12x4,air:13x5,air:14x4,normal:17x21,normal:18x21,fast:30x6,heavy:31x2,heavy:40x3,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x50,heavy:86x2,heavy:88x2,fast:98x5,medium:108x9,medium:123x9,heavy:127x3</t>
+          <t>L12 W24/25; N=180; EHP=48520.853183; air:2x10,air:11x8,air:12x8,air:13x10,air:14x8,fast:30x6,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x3,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x3,medium:83x9,medium:108x9,medium:123x9,normal:17x21,normal:18x21,swarm:84x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>10017684,10017694,10017686,10048588,10017693,10017687,10017701,10017684,10017694,10017686,10048588,10017693,10017687,10017684,10017694,10017686,10048588,10017693,10045175,10017684,10017694,10017686,10048588,10017693,10045175,10017684,10017694,10017686,10017681,10017693,10017690,10017684,10017694,10017688,10017681,10017693,10017690,10017684,10017694,10017688,10017681,10017693,10017691,10017684,10017694,10017688,10017681,10017693,10017691,10017684,10017694,10017688,10017681,10017693,10017691,10017684,10017694,10017688,10048589,10017698,10017692,10017684,10017694,10017688,10048589,10017698,10017692,10017684,10017694,10017689,10048589,10017698,10017695,10017684,10017694,10017689,10048589,10017698,10017695,10017684,10017694,10017689,10017682,10017698,10017696,10017684,10017694,10017689,10017682,10017698,10017696,10017684,10017694,10017689,10017682,10017698,10017700,10017684,10017694,10017697,10017682,10017698,10017700,10017684,10017694,10017697,10017682,10017698,10017700,10017684,10017694,10017697,10017683,10017699,10017684,10017694,10017697,10017683,10017699,10017684,10017694,10017697,10017683,10017699,10017684,10017694,10017697,10017683,10017699,10017685,10017694,10017699,10017685,10017694,10017699,10017685,10017694,10017699,10017685,10017694,10017699,10017685,10017694,10017699,10017685,10017694,10017685,10017694,10017685,10017694,10017685,10017694,10017685,10017694,10017685,10017694,10017685,10017694,10017685,10017694,10017685,10017694,10017685,10017694,10017685,10017694,10017685,10017694,10017685,10017694,10017685,10017694,10017685,10017694,10017685,10017694,10017685,10017694,10017694,10017694,10017694,10017694,10017694,10017694,10017694,10017694</t>
+          <t>10017684,10048588,10017686,10048588,10017693,10017687,10017701,10017684,10048588,10017686,10048588,10017693,10017687,10017684,10048588,10017686,10048588,10017693,10045175,10017684,10048588,10017686,10048588,10017693,10045175,10017684,10017681,10017686,10017681,10017693,10017690,10017684,10017681,10017688,10017681,10017693,10017690,10017684,10017681,10017688,10017681,10017693,10017691,10017684,10017681,10017688,10017681,10017693,10017691,10017684,10017681,10017688,10017681,10017693,10017691,10017684,10048589,10017688,10048589,10017698,10017692,10017684,10048589,10017688,10048589,10017698,10017692,10017684,10048589,10017689,10048589,10017698,10017695,10017684,10048589,10017689,10048589,10017698,10017695,10017684,10017682,10017689,10017682,10017698,10017696,10017684,10017682,10017689,10017682,10017698,10017696,10017684,10017682,10017689,10017682,10017698,10017700,10017684,10017682,10017697,10017682,10017698,10017700,10017684,10017682,10017697,10017682,10017698,10017700,10017684,10017683,10017697,10017683,10017699,10017684,10017683,10017697,10017683,10017699,10017684,10017683,10017697,10017683,10017699,10017684,10017683,10017697,10017683,10017699,10017685,10017694,10017699,10017685,10017694,10017699,10017685,10017694,10017699,10017685,10017694,10017699,10017685,10017694,10017699,10017685,10017694,10017685,10017694,10017685,10017694,10017685,10017694,10017685,10017694,10017685,10017694,10017685,10017694,10017685,10017694,10017685,10017694,10017685,10017694,10017685,10017694,10017685,10017694,10017685,10017694,10017685,10017694,10017685,10017694,10017685,10017694,10017685,10017694,10017694,10017694,10017694,10017694,10017694,10017694,10017694,10017694</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L12 W25/25; N=186; EHP=42288.000000; air:2x4,air:11x5,air:12x4,air:13x5,air:14x4,normal:17x22,normal:18x22,fast:30x5,heavy:31x2,heavy:40x2,fast:58x6,fast:64x5,heavy:67x2,heavy:70x3,heavy:80x2,medium:83x9,swarm:84x52,heavy:86x2,heavy:88x2,fast:98x6,medium:108x9,medium:123x9,heavy:127x3,boss:129x1</t>
+          <t>L12 W25/25; N=186; EHP=96797.200770; air:2x8,air:11x10,air:12x8,air:13x10,air:14x8,boss:129x1,fast:30x5,fast:58x6,fast:64x5,fast:98x6,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x3,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x3,medium:83x9,medium:108x9,medium:123x9,normal:17x22,normal:18x22,swarm:84x30 | manual: L1-scaled</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L12/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L12/EnemyList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>258</v>
+        <v>350</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>251</v>
+        <v>320</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>244</v>
+        <v>280</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>237</v>
+        <v>360</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>230</v>
+        <v>330</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>223</v>
+        <v>290</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>216</v>
+        <v>180</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>209</v>
+        <v>300</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>202</v>
+        <v>270</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>195</v>
+        <v>340</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>188</v>
+        <v>260</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>181</v>
+        <v>300</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>174</v>
+        <v>280</v>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>160</v>
+        <v>290</v>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>153</v>
+        <v>270</v>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>146</v>
+        <v>340</v>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>139</v>
+        <v>250</v>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>132</v>
+        <v>300</v>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>128</v>
+        <v>240</v>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>128</v>
+        <v>290</v>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>128</v>
+        <v>270</v>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>128</v>
+        <v>360</v>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>128</v>
+        <v>180</v>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
